--- a/docs/transportation/data/funding_ledger.xlsx
+++ b/docs/transportation/data/funding_ledger.xlsx
@@ -5369,7 +5369,7 @@
       </c>
       <c r="M64" s="8" t="inlineStr">
         <is>
-          <t>Project Cost Estimate table, p.6</t>
+          <t>Project Cost Estimate table, p.5</t>
         </is>
       </c>
       <c r="N64" s="8" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="M65" s="8" t="inlineStr">
         <is>
-          <t>Project Cost Estimate and Funding Plan tables, pp.6-7</t>
+          <t>Project Cost Estimate (p.5) and Funding Plan (pp.5-6)</t>
         </is>
       </c>
       <c r="N65" s="8" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="M67" s="8" t="inlineStr">
         <is>
-          <t>Project Cost Estimate table, p.6</t>
+          <t>Project Cost Estimate table, p.5</t>
         </is>
       </c>
       <c r="N67" s="8" t="inlineStr">
